--- a/src/test/resources/filters_personal_details/filters_age.xlsx
+++ b/src/test/resources/filters_personal_details/filters_age.xlsx
@@ -8,14 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\Eticaa Project Automation\Eticaa-Automation\src\test\resources\filters_personal_details\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5DB8DD-75B3-4B31-8C9A-BA87B4DE4743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F00D94-B0AD-4F86-9CDE-C8DE40534383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Locations" sheetId="1" r:id="rId1"/>
+    <sheet name="AgeFilters" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -377,10 +388,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -388,7 +399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>0</v>
       </c>
@@ -396,12 +407,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>45</v>
       </c>
@@ -409,7 +420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>20</v>
       </c>
@@ -417,17 +428,17 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>80</v>
       </c>
@@ -435,7 +446,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -443,20 +454,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>30</v>
       </c>
@@ -464,7 +475,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>16</v>
       </c>
@@ -472,7 +483,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>78</v>
       </c>
@@ -480,7 +491,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>10</v>
       </c>
@@ -488,7 +499,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>0</v>
       </c>
@@ -496,12 +507,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>70</v>
       </c>
@@ -509,12 +520,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>3</v>
       </c>
@@ -522,7 +533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>14</v>
       </c>
@@ -530,17 +541,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>25</v>
       </c>
@@ -548,17 +559,17 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>12</v>
       </c>
@@ -566,20 +577,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>33</v>
       </c>
       <c r="B29">
         <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>8</v>
-      </c>
-      <c r="B30">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
